--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N32_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>8.896349550612314</v>
       </c>
       <c r="E2" t="n">
-        <v>14.00601174155511</v>
+        <v>15.6784650067454</v>
       </c>
       <c r="F2" t="n">
-        <v>11.05821518107855</v>
+        <v>12.73924948011251</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>0.3401588394472127</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8903107743141908</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.6784650067454</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.73924948011251</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0035F0001T0006Z000C1N32.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>37.09829350703037</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>31.01277991276941</v>
       </c>
-      <c r="E3" t="n">
-        <v>14.00601174155511</v>
-      </c>
-      <c r="F3" t="n">
-        <v>11.05821518107855</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>15.6784650067454</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.73924948011251</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.086270023920145</v>
+        <v>1.476518878887024</v>
       </c>
       <c r="D2" t="n">
-        <v>8.896349550612314</v>
+        <v>1.445656801974501</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6784650067454</v>
+        <v>2.547750563596127</v>
       </c>
       <c r="F2" t="n">
-        <v>12.73924948011251</v>
+        <v>2.070128040518282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3401588394472127</v>
+        <v>0.05527581141017206</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8903107743141908</v>
+        <v>0.144675500826056</v>
       </c>
       <c r="E3" t="n">
-        <v>15.6784650067454</v>
+        <v>2.547750563596127</v>
       </c>
       <c r="F3" t="n">
-        <v>12.73924948011251</v>
+        <v>2.070128040518282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.09829350703037</v>
+        <v>6.028472694892435</v>
       </c>
       <c r="D4" t="n">
-        <v>31.01277991276941</v>
+        <v>5.03957673582503</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6784650067454</v>
+        <v>2.547750563596127</v>
       </c>
       <c r="F4" t="n">
-        <v>12.73924948011251</v>
+        <v>2.070128040518282</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
